--- a/modulo-i/comandos.xlsx
+++ b/modulo-i/comandos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tardes\Desktop\compartida\modulo-i\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C3D52A-E20B-4127-8349-645444F624DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA3A554-EDE0-458F-ABB5-30D85B775EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F428F6BA-8206-4B6F-8A69-AAE733F78341}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F428F6BA-8206-4B6F-8A69-AAE733F78341}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>CMD</t>
   </si>
@@ -62,9 +62,6 @@
     <t>dir /a</t>
   </si>
   <si>
-    <t>la -la</t>
-  </si>
-  <si>
     <t>incluye elementos ocultos</t>
   </si>
   <si>
@@ -129,6 +126,123 @@
   </si>
   <si>
     <t>git commit -m"mensaje"</t>
+  </si>
+  <si>
+    <t>configurar nombre usuario</t>
+  </si>
+  <si>
+    <t>configurar email usario</t>
+  </si>
+  <si>
+    <t>crear repositorio local</t>
+  </si>
+  <si>
+    <t>consultar el estado del repositorio</t>
+  </si>
+  <si>
+    <t>agregar ficheros del working directory a la staging area</t>
+  </si>
+  <si>
+    <t>confirmar (commit) los cambios de la staging area</t>
+  </si>
+  <si>
+    <t>git log</t>
+  </si>
+  <si>
+    <t>consultar historial</t>
+  </si>
+  <si>
+    <t>git --version</t>
+  </si>
+  <si>
+    <t>consultar version git</t>
+  </si>
+  <si>
+    <t>git config --list</t>
+  </si>
+  <si>
+    <t>consultar configuración</t>
+  </si>
+  <si>
+    <t>ssh-keygen -t ed25519 -C "email"</t>
+  </si>
+  <si>
+    <t>genera clave ssh</t>
+  </si>
+  <si>
+    <t>type %USERPROFILE%\.ssh\id_ed25519.put</t>
+  </si>
+  <si>
+    <t>consultar clave pública</t>
+  </si>
+  <si>
+    <t>git remote add origin XXXXXX</t>
+  </si>
+  <si>
+    <t>vincular el repo local con GitHub</t>
+  </si>
+  <si>
+    <t>git push -u origin main</t>
+  </si>
+  <si>
+    <t>subir ficheros a GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rename </t>
+  </si>
+  <si>
+    <t>renombrar objeto</t>
+  </si>
+  <si>
+    <t>ls -la</t>
+  </si>
+  <si>
+    <t>git add fich.txt / git add .</t>
+  </si>
+  <si>
+    <t>git diff</t>
+  </si>
+  <si>
+    <t>compara el estado del working directory con el ultimo commit</t>
+  </si>
+  <si>
+    <t>git checkout &lt;id&gt;</t>
+  </si>
+  <si>
+    <t>posiciona el HEAD en el commit &lt;id&gt;</t>
+  </si>
+  <si>
+    <t>cls</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>borrar pantalla</t>
+  </si>
+  <si>
+    <t>git switch main</t>
+  </si>
+  <si>
+    <t>posiciona el HEAD en el commit main</t>
+  </si>
+  <si>
+    <t>git config --global alias.&lt;alias&gt; "comando git"</t>
+  </si>
+  <si>
+    <t>cra un alias llamado &lt;alias&gt; para el "comando git"</t>
+  </si>
+  <si>
+    <t>git remote -v</t>
+  </si>
+  <si>
+    <t>consultar el repo remoto asociado</t>
+  </si>
+  <si>
+    <t>code .</t>
+  </si>
+  <si>
+    <t>abrir VSC en direct. Actual</t>
   </si>
 </sst>
 </file>
@@ -203,7 +317,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -519,25 +633,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32AB220-30CE-4048-8A34-A084F7E7AEF4}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.140625" customWidth="1"/>
+    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -547,100 +665,235 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
       <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
